--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:02</t>
+    <t xml:space="preserve">2026-09-09 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:35</t>
+    <t xml:space="preserve">2026-09-16 16:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
@@ -6,29 +6,32 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comunas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edades'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comunas'!$A$1:$D$12</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo migratorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t xml:space="preserve">Cambiaron de comuna dentro de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzaron el límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se fueron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la región</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -40,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 16:35</t>
+    <t xml:space="preserve">2026-09-30 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -58,31 +61,64 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">M_SALDOMIGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Región de Magallanes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 a 4 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 a 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 29 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 a 59 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 años o más</t>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras comunas de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punta Arenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo de Hornos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timaukel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Gregorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laguna Blanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torres del Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antártica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natales</t>
   </si>
 </sst>
 </file>
@@ -447,8 +483,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,25 +497,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="n">
+        <v>2549</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>37</v>
+        <v>14341</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>7139</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -493,58 +542,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -558,60 +607,182 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="18.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-21</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>51</v>
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>204</v>
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-91</v>
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-80</v>
+        <v>-6</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>-14</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>-34</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>-62</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>-105</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2024_magallanes.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 09:57</t>
+    <t xml:space="preserve">2026-10-05 03:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
